--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/aysen.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/aysen.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>152106.33</v>
+        <v>152778.42</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>40126.4</v>
+        <v>40131.31</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>10767.36</v>
+        <v>10932.63</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>10638.47</v>
+        <v>10468.71</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/aysen.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>734-980-CM25</t>
+          <t>868-264-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>72.222.000-5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>GOBIERNO REGIONAL DE AYSEN</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>NEUROCLICK MARKETING DIGITAL SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
+          <t>77.240.269-4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>152778.42</v>
+        <v>9774.549999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4610-30-CM26</t>
+          <t>734-980-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>40131.31</v>
+        <v>152778.42</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>734-394-CM26</t>
+          <t>4610-30-CM26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>69.240.400-9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>ZECOVERY LTDA   -    EXEC</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>76.260.080-3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>10932.63</v>
+        <v>40131.31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1233615-1196-CM26</t>
+          <t>734-394-CM26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
+          <t>76.304.354-1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,6 +752,67 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
+        <v>10932.63</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1233615-1196-CM26</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>61.980.950-5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Aysén</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ZECOVERY LTDA   -    EXEC</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>10468.71</v>
       </c>
     </row>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/aysen.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/aysen.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aysén" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Aysén" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>868-264-CM25</t>
+          <t>1068243-23-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>72.222.000-5</t>
+          <t>61.979.830-9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE AYSEN</t>
+          <t>SUBSECRETARIA DE ENERGIA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>NEUROCLICK MARKETING DIGITAL SPA</t>
+          <t>PAULA ALEJANDRA QUITRAL HERRERA, SERVICIOS INFORMATICOS, EMPRESA INDIV</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.240.269-4</t>
+          <t>76.092.019-3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>9774.549999999999</v>
+        <v>23883.73</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>734-980-CM25</t>
+          <t>1068243-49-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>61.979.830-9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>SUBSECRETARIA DE ENERGIA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>METASOFT SOCIEDAD POR ACCIONES</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
+          <t>76.213.064-5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>152778.42</v>
+        <v>34341.67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4610-30-CM26</t>
+          <t>1233615-1241-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>NAPSIS SPA.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
+          <t>76.093.358-9</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>40131.31</v>
+        <v>16721.39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>734-394-CM26</t>
+          <t>868-264-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>72.222.000-5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>GOBIERNO REGIONAL DE AYSEN</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>NEUROCLICK MARKETING DIGITAL SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>77.240.269-4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>10932.63</v>
+        <v>9774.549999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1233615-1196-CM26</t>
+          <t>734-980-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,6 +813,189 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
+        <v>152778.42</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4610-30-CM26</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>69.240.400-9</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ZECOVERY LTDA   -    EXEC</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>40131.31</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>734-394-CM26</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>61.607.800-3</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>10932.63</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1233615-1196-CM26</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>61.980.950-5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Aysén</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ZECOVERY LTDA   -    EXEC</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
         <v>10468.71</v>
       </c>
     </row>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/aysen.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -798,7 +798,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -880,7 +880,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>734-394-CM26</t>
+          <t>1068243-2-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,22 +895,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>61.979.830-9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>SUBSECRETARIA DE ENERGIA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>10932.63</v>
+        <v>17430.13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1233615-1196-CM26</t>
+          <t>734-394-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ZECOVERY LTDA   -    EXEC</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.260.080-3</t>
+          <t>76.304.354-1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,7 +996,190 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
+        <v>10932.63</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1068243-3-CM26</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>61.979.830-9</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE ENERGIA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SAARGO SPA</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>76.891.821-k</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>18480.71</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1233615-1196-CM26</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>61.980.950-5</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Aysén</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Zecovery Ltda   -    EXEC</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
         <v>10468.71</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1233615-1544-CM26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>61.980.950-5</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Aysén</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>76.334.381-2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>13789.98</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/aysen.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/aysen.xlsx
@@ -562,7 +562,11 @@
           <t>76.092.019-3</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +810,11 @@
           <t>76.260.080-3</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +875,11 @@
           <t>76.260.080-3</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1001,11 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1066,11 @@
           <t>76.891.821-k</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1131,11 @@
           <t>76.260.080-3</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1196,11 @@
           <t>76.334.381-2</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/aysen.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/aysen.xlsx
@@ -973,7 +973,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
